--- a/data/trans_bre/P1416-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1416-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,19</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-37,65%</t>
+          <t>-23,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,94</t>
+          <t>-0,6; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,97</t>
+          <t>-3,78; 3,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,38</t>
+          <t>-5,11; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 1,68</t>
+          <t>-10,76; 3,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 103,75</t>
+          <t>-6,86; 100,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 58,34</t>
+          <t>-33,44; 56,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 40,48</t>
+          <t>-40,7; 38,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,98; 15,4</t>
+          <t>-57,63; 38,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,91</t>
+          <t>-1,0; 5,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,66</t>
+          <t>-0,83; 5,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,13</t>
+          <t>0,04; 6,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,04</t>
+          <t>-2,3; 7,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 87,09</t>
+          <t>-11,04; 83,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 90,12</t>
+          <t>-10,83; 102,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 117,08</t>
+          <t>-1,47; 118,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 54,81</t>
+          <t>-17,14; 89,4</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,45</t>
+          <t>0,81; 7,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,59</t>
+          <t>1,51; 7,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,96</t>
+          <t>2,31; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,11</t>
+          <t>-2,8; 3,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 141,79</t>
+          <t>10,49; 133,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,9; 157,61</t>
+          <t>18,89; 159,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,66; 226,92</t>
+          <t>34,29; 212,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 35,89</t>
+          <t>-21,62; 39,77</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,7</t>
+          <t>0,97; 7,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,62</t>
+          <t>1,26; 6,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,1</t>
+          <t>1,63; 7,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,97</t>
+          <t>1,2; 7,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 185,72</t>
+          <t>12,5; 194,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,02; 425,49</t>
+          <t>24,4; 374,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,2; 296,78</t>
+          <t>35,57; 284,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 313,71</t>
+          <t>9,12; 88,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,51</t>
+          <t>-2,72; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,54</t>
+          <t>-1,89; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,14</t>
+          <t>0,68; 7,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,12</t>
+          <t>0,65; 6,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 96,39</t>
+          <t>-35,03; 97,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 145,1</t>
+          <t>-40,3; 162,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 269,91</t>
+          <t>8,37; 257,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 110,63</t>
+          <t>5,93; 104,92</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,02</t>
+          <t>1,39; 9,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,26</t>
+          <t>-3,43; 3,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,49</t>
+          <t>0,12; 4,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,12</t>
+          <t>1,64; 7,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,21; 308,26</t>
+          <t>16,85; 332,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,32; 155,38</t>
+          <t>-59,41; 142,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 896,72</t>
+          <t>-12,36; 751,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 101,58</t>
+          <t>18,88; 169,95</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,79</t>
+          <t>-3,17; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,2</t>
+          <t>-1,89; 5,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,9</t>
+          <t>-1,45; 4,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,65</t>
+          <t>-0,07; 5,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,32; 160,12</t>
+          <t>-55,59; 179,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 314,4</t>
+          <t>-36,89; 293,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 244,03</t>
+          <t>-38,99; 235,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 141,27</t>
+          <t>-1,98; 149,5</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,21</t>
+          <t>1,51; 4,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,39</t>
+          <t>1,08; 3,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,21</t>
+          <t>1,78; 4,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,48</t>
+          <t>0,81; 3,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,84; 69,12</t>
+          <t>21,13; 68,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,87; 72,17</t>
+          <t>18,22; 74,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,34; 94,45</t>
+          <t>31,45; 93,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 43,74</t>
+          <t>7,61; 42,38</t>
         </is>
       </c>
     </row>
